--- a/api/templates/export/results/es.xlsx
+++ b/api/templates/export/results/es.xlsx
@@ -1,16 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="21126"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
+  <fileVersion appName="xl" lastEdited="6" lowestEdited="5" rupBuild="14420"/>
   <workbookPr showInkAnnotation="0" autoCompressPictures="0"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="\\wsl$\Ubuntu-20.04\home\ubuntu\aspect\api\templates\export\results\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\PROJECTS_2020\SystemOne\aspect\api\templates\export\results\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BC314E9F-757B-425B-8D50-CA39FE382DE1}" xr6:coauthVersionLast="40" xr6:coauthVersionMax="40" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="480" yWindow="480" windowWidth="20734" windowHeight="11760" tabRatio="815" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="480" yWindow="480" windowWidth="20736" windowHeight="11760" tabRatio="815"/>
   </bookViews>
   <sheets>
     <sheet name="Results" sheetId="1" r:id="rId1"/>
@@ -26,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="71" uniqueCount="49">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="77" uniqueCount="55">
   <si>
     <t>Code</t>
   </si>
@@ -173,12 +172,30 @@
   </si>
   <si>
     <t>ID de Paciente</t>
+  </si>
+  <si>
+    <t>&lt;sampleId&gt;</t>
+  </si>
+  <si>
+    <t>&lt;assayName&gt;</t>
+  </si>
+  <si>
+    <t>&lt;resultText&gt;</t>
+  </si>
+  <si>
+    <t>Muestra ID</t>
+  </si>
+  <si>
+    <t>Ensayo</t>
+  </si>
+  <si>
+    <t>Texto de resultado</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9" mc:Ignorable="x14ac x16r2 xr xr9">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
   <fonts count="6" x14ac:knownFonts="1">
     <font>
       <sz val="12"/>
@@ -242,7 +259,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="4">
     <border>
       <left/>
       <right/>
@@ -265,6 +282,32 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top/>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="43">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
@@ -311,7 +354,7 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="20">
+  <cellXfs count="25">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
@@ -366,6 +409,21 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -439,7 +497,7 @@
     </dxf>
   </dxfs>
   <tableStyles count="1" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleMedium4">
-    <tableStyle name="MySqlDefault" pivot="0" table="0" count="2" xr9:uid="{00000000-0011-0000-FFFF-FFFF00000000}">
+    <tableStyle name="MySqlDefault" pivot="0" table="0" count="2">
       <tableStyleElement type="wholeTable" dxfId="1"/>
       <tableStyleElement type="headerRow" dxfId="0"/>
     </tableStyle>
@@ -776,24 +834,26 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:F9"/>
-  <sheetFormatPr defaultColWidth="11" defaultRowHeight="15.9" x14ac:dyDescent="0.45"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="A1:I9"/>
+  <sheetFormatPr defaultColWidth="11" defaultRowHeight="15.6" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="22.5" style="5" customWidth="1"/>
-    <col min="2" max="2" width="23.140625" style="7" customWidth="1"/>
-    <col min="3" max="3" width="22.35546875" style="8" customWidth="1"/>
+    <col min="2" max="2" width="23.09765625" style="7" customWidth="1"/>
+    <col min="3" max="3" width="22.3984375" style="8" customWidth="1"/>
     <col min="4" max="4" width="18.5" style="8" customWidth="1"/>
-    <col min="5" max="5" width="28.640625" style="9" customWidth="1"/>
-    <col min="6" max="6" width="20.7109375" style="9" customWidth="1"/>
+    <col min="5" max="5" width="28.59765625" style="9" customWidth="1"/>
+    <col min="6" max="6" width="21.3984375" style="9" customWidth="1"/>
+    <col min="7" max="8" width="21.296875" style="9" customWidth="1"/>
+    <col min="9" max="9" width="20.69921875" style="9" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" ht="20.6" x14ac:dyDescent="0.55000000000000004">
+    <row r="1" spans="1:9" ht="21" x14ac:dyDescent="0.4">
       <c r="A1" s="6" t="s">
         <v>40</v>
       </c>
     </row>
-    <row r="2" spans="1:6" s="5" customFormat="1" x14ac:dyDescent="0.45">
+    <row r="2" spans="1:9" s="5" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A2" s="5" t="s">
         <v>41</v>
       </c>
@@ -802,15 +862,21 @@
       <c r="D2" s="8"/>
       <c r="E2" s="7"/>
       <c r="F2" s="7"/>
-    </row>
-    <row r="3" spans="1:6" s="5" customFormat="1" x14ac:dyDescent="0.45">
+      <c r="G2" s="7"/>
+      <c r="H2" s="7"/>
+      <c r="I2" s="7"/>
+    </row>
+    <row r="3" spans="1:9" s="5" customFormat="1" x14ac:dyDescent="0.3">
       <c r="B3" s="7"/>
       <c r="C3" s="8"/>
       <c r="D3" s="8"/>
       <c r="E3" s="7"/>
       <c r="F3" s="7"/>
-    </row>
-    <row r="4" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="G3" s="7"/>
+      <c r="H3" s="7"/>
+      <c r="I3" s="7"/>
+    </row>
+    <row r="4" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A4" s="5" t="s">
         <v>33</v>
       </c>
@@ -818,7 +884,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="5" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="5" spans="1:9" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A5" s="19" t="s">
         <v>42</v>
       </c>
@@ -828,11 +894,20 @@
       <c r="C5" s="18"/>
       <c r="D5" s="18"/>
       <c r="E5" s="18"/>
-      <c r="F5" s="17" t="s">
+      <c r="F5" s="20" t="s">
+        <v>52</v>
+      </c>
+      <c r="G5" s="20" t="s">
+        <v>53</v>
+      </c>
+      <c r="H5" s="20" t="s">
+        <v>54</v>
+      </c>
+      <c r="I5" s="23" t="s">
         <v>48</v>
       </c>
     </row>
-    <row r="6" spans="1:6" s="4" customFormat="1" ht="31.5" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="6" spans="1:9" s="4" customFormat="1" ht="31.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A6" s="18"/>
       <c r="B6" s="15" t="s">
         <v>44</v>
@@ -846,9 +921,12 @@
       <c r="E6" s="15" t="s">
         <v>47</v>
       </c>
-      <c r="F6" s="18"/>
-    </row>
-    <row r="7" spans="1:6" s="2" customFormat="1" x14ac:dyDescent="0.45">
+      <c r="F6" s="21"/>
+      <c r="G6" s="21"/>
+      <c r="H6" s="22"/>
+      <c r="I6" s="24"/>
+    </row>
+    <row r="7" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A7" s="16" t="s">
         <v>36</v>
       </c>
@@ -864,20 +942,35 @@
       <c r="E7" s="11" t="s">
         <v>38</v>
       </c>
-      <c r="F7" s="12" t="s">
+      <c r="F7" s="11" t="s">
+        <v>49</v>
+      </c>
+      <c r="G7" s="11" t="s">
+        <v>50</v>
+      </c>
+      <c r="H7" s="11" t="s">
+        <v>51</v>
+      </c>
+      <c r="I7" s="12" t="s">
         <v>39</v>
       </c>
     </row>
-    <row r="9" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="9" spans="1:9" x14ac:dyDescent="0.3">
       <c r="C9" s="13"/>
       <c r="D9" s="13"/>
       <c r="E9" s="14"/>
+      <c r="F9" s="14"/>
+      <c r="G9" s="14"/>
+      <c r="H9" s="14"/>
     </row>
   </sheetData>
-  <mergeCells count="3">
+  <mergeCells count="6">
+    <mergeCell ref="I5:I6"/>
     <mergeCell ref="F5:F6"/>
     <mergeCell ref="B5:E5"/>
     <mergeCell ref="A5:A6"/>
+    <mergeCell ref="G5:G6"/>
+    <mergeCell ref="H5:H6"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup orientation="portrait" horizontalDpi="4294967292" verticalDpi="4294967292" r:id="rId1"/>
@@ -890,16 +983,16 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:C27"/>
-  <sheetFormatPr defaultColWidth="8.640625" defaultRowHeight="22" customHeight="1" x14ac:dyDescent="0.45"/>
+  <sheetFormatPr defaultColWidth="8.59765625" defaultRowHeight="22.05" customHeight="1" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="5.140625" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="39.2109375" customWidth="1"/>
-    <col min="3" max="3" width="100.640625" customWidth="1"/>
+    <col min="1" max="1" width="5.09765625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="39.19921875" customWidth="1"/>
+    <col min="3" max="3" width="100.59765625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" ht="22" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="1" spans="1:3" ht="22.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -910,7 +1003,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:3" ht="22" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="2" spans="1:3" ht="22.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A2" s="3">
         <v>1001</v>
       </c>
@@ -921,7 +1014,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="3" spans="1:3" ht="22" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="3" spans="1:3" ht="22.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A3" s="3">
         <v>1002</v>
       </c>
@@ -932,7 +1025,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="4" spans="1:3" ht="22" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="4" spans="1:3" ht="22.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A4" s="3">
         <v>1004</v>
       </c>
@@ -943,7 +1036,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="5" spans="1:3" ht="22" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="5" spans="1:3" ht="22.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A5" s="3">
         <v>1005</v>
       </c>
@@ -954,7 +1047,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="6" spans="1:3" ht="22" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="6" spans="1:3" ht="22.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A6" s="3">
         <v>1006</v>
       </c>
@@ -965,7 +1058,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="7" spans="1:3" ht="22" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="7" spans="1:3" ht="22.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A7" s="3">
         <v>1007</v>
       </c>
@@ -976,7 +1069,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="8" spans="1:3" ht="22" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="8" spans="1:3" ht="22.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A8" s="3">
         <v>1017</v>
       </c>
@@ -987,7 +1080,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="9" spans="1:3" ht="22" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="9" spans="1:3" ht="22.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A9" s="3">
         <v>1018</v>
       </c>
@@ -998,7 +1091,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="10" spans="1:3" ht="22" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="10" spans="1:3" ht="22.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A10" s="3">
         <v>2003</v>
       </c>
@@ -1009,7 +1102,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="11" spans="1:3" ht="22" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="11" spans="1:3" ht="22.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A11" s="3">
         <v>2005</v>
       </c>
@@ -1020,7 +1113,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="12" spans="1:3" ht="22" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="12" spans="1:3" ht="22.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A12" s="3">
         <v>2008</v>
       </c>
@@ -1031,7 +1124,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="13" spans="1:3" ht="22" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="13" spans="1:3" ht="22.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A13" s="3">
         <v>2009</v>
       </c>
@@ -1042,7 +1135,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="14" spans="1:3" ht="22" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="14" spans="1:3" ht="22.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A14" s="3">
         <v>2011</v>
       </c>
@@ -1053,7 +1146,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="15" spans="1:3" ht="22" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="15" spans="1:3" ht="22.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A15" s="3">
         <v>2014</v>
       </c>
@@ -1064,7 +1157,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="16" spans="1:3" ht="22" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="16" spans="1:3" ht="22.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A16" s="3">
         <v>2016</v>
       </c>
@@ -1075,7 +1168,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="17" spans="1:3" ht="22" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="17" spans="1:3" ht="22.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A17" s="3">
         <v>2018</v>
       </c>
@@ -1086,7 +1179,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="18" spans="1:3" ht="22" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="18" spans="1:3" ht="22.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A18" s="3">
         <v>2022</v>
       </c>
@@ -1097,7 +1190,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="19" spans="1:3" ht="22" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="19" spans="1:3" ht="22.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A19" s="3">
         <v>2025</v>
       </c>
@@ -1108,7 +1201,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="20" spans="1:3" ht="22" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="20" spans="1:3" ht="22.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A20" s="3">
         <v>2032</v>
       </c>
@@ -1119,7 +1212,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="21" spans="1:3" ht="22" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="21" spans="1:3" ht="22.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A21" s="3">
         <v>2034</v>
       </c>
@@ -1130,7 +1223,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="22" spans="1:3" ht="22" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="22" spans="1:3" ht="22.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A22" s="3">
         <v>2037</v>
       </c>
@@ -1141,7 +1234,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="23" spans="1:3" ht="22" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="23" spans="1:3" ht="22.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A23" s="3">
         <v>4010</v>
       </c>
@@ -1152,7 +1245,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="24" spans="1:3" ht="22" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="24" spans="1:3" ht="22.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A24" s="3">
         <v>4017</v>
       </c>
@@ -1163,7 +1256,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="25" spans="1:3" ht="22" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="25" spans="1:3" ht="22.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A25" s="3">
         <v>5006</v>
       </c>
@@ -1174,7 +1267,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="26" spans="1:3" ht="22" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="26" spans="1:3" ht="22.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A26" s="3">
         <v>5007</v>
       </c>
@@ -1185,7 +1278,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="27" spans="1:3" ht="22" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="27" spans="1:3" ht="22.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A27" s="3">
         <v>5011</v>
       </c>

--- a/api/templates/export/results/es.xlsx
+++ b/api/templates/export/results/es.xlsx
@@ -5,7 +5,7 @@
   <workbookPr showInkAnnotation="0" autoCompressPictures="0"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\PROJECTS_2020\SystemOne\aspect\api\templates\export\results\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\PROJECTS_2020\SystemOne\aspect-node-12\api\templates\export\results\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="77" uniqueCount="55">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="81" uniqueCount="59">
   <si>
     <t>Code</t>
   </si>
@@ -190,6 +190,18 @@
   </si>
   <si>
     <t>Texto de resultado</t>
+  </si>
+  <si>
+    <t>&lt;resultWorkflowStatus&gt;</t>
+  </si>
+  <si>
+    <t>&lt;resultTreatmentStatus&gt;</t>
+  </si>
+  <si>
+    <t>Estado del flujo de trabajo</t>
+  </si>
+  <si>
+    <t>Estado del tratamiento</t>
   </si>
 </sst>
 </file>
@@ -354,7 +366,7 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="25">
+  <cellXfs count="26">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
@@ -402,6 +414,18 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -411,20 +435,11 @@
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="43">
@@ -835,7 +850,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:I9"/>
+  <dimension ref="A1:K9"/>
   <sheetFormatPr defaultColWidth="11" defaultRowHeight="15.6" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="22.5" style="5" customWidth="1"/>
@@ -845,15 +860,17 @@
     <col min="5" max="5" width="28.59765625" style="9" customWidth="1"/>
     <col min="6" max="6" width="21.3984375" style="9" customWidth="1"/>
     <col min="7" max="8" width="21.296875" style="9" customWidth="1"/>
-    <col min="9" max="9" width="20.69921875" style="9" customWidth="1"/>
+    <col min="9" max="9" width="19" style="9" customWidth="1"/>
+    <col min="10" max="10" width="18.3984375" style="9" customWidth="1"/>
+    <col min="11" max="11" width="20.69921875" style="9" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9" ht="21" x14ac:dyDescent="0.4">
+    <row r="1" spans="1:11" ht="21" x14ac:dyDescent="0.4">
       <c r="A1" s="6" t="s">
         <v>40</v>
       </c>
     </row>
-    <row r="2" spans="1:9" s="5" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:11" s="5" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A2" s="5" t="s">
         <v>41</v>
       </c>
@@ -865,8 +882,10 @@
       <c r="G2" s="7"/>
       <c r="H2" s="7"/>
       <c r="I2" s="7"/>
-    </row>
-    <row r="3" spans="1:9" s="5" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="J2" s="7"/>
+      <c r="K2" s="7"/>
+    </row>
+    <row r="3" spans="1:11" s="5" customFormat="1" x14ac:dyDescent="0.3">
       <c r="B3" s="7"/>
       <c r="C3" s="8"/>
       <c r="D3" s="8"/>
@@ -875,8 +894,10 @@
       <c r="G3" s="7"/>
       <c r="H3" s="7"/>
       <c r="I3" s="7"/>
-    </row>
-    <row r="4" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="J3" s="7"/>
+      <c r="K3" s="7"/>
+    </row>
+    <row r="4" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A4" s="5" t="s">
         <v>33</v>
       </c>
@@ -884,31 +905,37 @@
         <v>2</v>
       </c>
     </row>
-    <row r="5" spans="1:9" ht="30" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A5" s="19" t="s">
+    <row r="5" spans="1:11" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A5" s="23" t="s">
         <v>42</v>
       </c>
-      <c r="B5" s="17" t="s">
+      <c r="B5" s="21" t="s">
         <v>43</v>
       </c>
-      <c r="C5" s="18"/>
-      <c r="D5" s="18"/>
-      <c r="E5" s="18"/>
-      <c r="F5" s="20" t="s">
+      <c r="C5" s="22"/>
+      <c r="D5" s="22"/>
+      <c r="E5" s="22"/>
+      <c r="F5" s="19" t="s">
         <v>52</v>
       </c>
-      <c r="G5" s="20" t="s">
+      <c r="G5" s="19" t="s">
         <v>53</v>
       </c>
-      <c r="H5" s="20" t="s">
+      <c r="H5" s="19" t="s">
         <v>54</v>
       </c>
-      <c r="I5" s="23" t="s">
+      <c r="I5" s="19" t="s">
+        <v>57</v>
+      </c>
+      <c r="J5" s="19" t="s">
+        <v>58</v>
+      </c>
+      <c r="K5" s="17" t="s">
         <v>48</v>
       </c>
     </row>
-    <row r="6" spans="1:9" s="4" customFormat="1" ht="31.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A6" s="18"/>
+    <row r="6" spans="1:11" s="4" customFormat="1" ht="31.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A6" s="22"/>
       <c r="B6" s="15" t="s">
         <v>44</v>
       </c>
@@ -921,12 +948,14 @@
       <c r="E6" s="15" t="s">
         <v>47</v>
       </c>
-      <c r="F6" s="21"/>
-      <c r="G6" s="21"/>
-      <c r="H6" s="22"/>
+      <c r="F6" s="20"/>
+      <c r="G6" s="20"/>
+      <c r="H6" s="24"/>
       <c r="I6" s="24"/>
-    </row>
-    <row r="7" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="J6" s="24"/>
+      <c r="K6" s="18"/>
+    </row>
+    <row r="7" spans="1:11" s="2" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A7" s="16" t="s">
         <v>36</v>
       </c>
@@ -951,26 +980,36 @@
       <c r="H7" s="11" t="s">
         <v>51</v>
       </c>
-      <c r="I7" s="12" t="s">
+      <c r="I7" s="25" t="s">
+        <v>55</v>
+      </c>
+      <c r="J7" s="25" t="s">
+        <v>56</v>
+      </c>
+      <c r="K7" s="12" t="s">
         <v>39</v>
       </c>
     </row>
-    <row r="9" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:11" x14ac:dyDescent="0.3">
       <c r="C9" s="13"/>
       <c r="D9" s="13"/>
       <c r="E9" s="14"/>
       <c r="F9" s="14"/>
       <c r="G9" s="14"/>
       <c r="H9" s="14"/>
+      <c r="I9" s="14"/>
+      <c r="J9" s="14"/>
     </row>
   </sheetData>
-  <mergeCells count="6">
-    <mergeCell ref="I5:I6"/>
+  <mergeCells count="8">
+    <mergeCell ref="K5:K6"/>
     <mergeCell ref="F5:F6"/>
     <mergeCell ref="B5:E5"/>
     <mergeCell ref="A5:A6"/>
     <mergeCell ref="G5:G6"/>
     <mergeCell ref="H5:H6"/>
+    <mergeCell ref="I5:I6"/>
+    <mergeCell ref="J5:J6"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup orientation="portrait" horizontalDpi="4294967292" verticalDpi="4294967292" r:id="rId1"/>

--- a/api/templates/export/results/es.xlsx
+++ b/api/templates/export/results/es.xlsx
@@ -5,7 +5,7 @@
   <workbookPr showInkAnnotation="0" autoCompressPictures="0"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\PROJECTS_2020\SystemOne\aspect-node-12\api\templates\export\results\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\PROJECTS_2020\SystemOne\aspect\api\templates\export\results\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
@@ -165,9 +165,6 @@
     <t>Ciudad</t>
   </si>
   <si>
-    <t>Sitio</t>
-  </si>
-  <si>
     <t>Dispositivo</t>
   </si>
   <si>
@@ -202,6 +199,9 @@
   </si>
   <si>
     <t>Estado del tratamiento</t>
+  </si>
+  <si>
+    <t>Sitio de recolección de muestras</t>
   </si>
 </sst>
 </file>
@@ -414,6 +414,9 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -437,9 +440,6 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="43">
@@ -906,36 +906,36 @@
       </c>
     </row>
     <row r="5" spans="1:11" ht="30" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A5" s="23" t="s">
+      <c r="A5" s="24" t="s">
         <v>42</v>
       </c>
-      <c r="B5" s="21" t="s">
+      <c r="B5" s="22" t="s">
         <v>43</v>
       </c>
-      <c r="C5" s="22"/>
-      <c r="D5" s="22"/>
-      <c r="E5" s="22"/>
-      <c r="F5" s="19" t="s">
+      <c r="C5" s="23"/>
+      <c r="D5" s="23"/>
+      <c r="E5" s="23"/>
+      <c r="F5" s="20" t="s">
+        <v>51</v>
+      </c>
+      <c r="G5" s="20" t="s">
         <v>52</v>
       </c>
-      <c r="G5" s="19" t="s">
+      <c r="H5" s="20" t="s">
         <v>53</v>
       </c>
-      <c r="H5" s="19" t="s">
-        <v>54</v>
-      </c>
-      <c r="I5" s="19" t="s">
+      <c r="I5" s="20" t="s">
+        <v>56</v>
+      </c>
+      <c r="J5" s="20" t="s">
         <v>57</v>
       </c>
-      <c r="J5" s="19" t="s">
-        <v>58</v>
-      </c>
-      <c r="K5" s="17" t="s">
-        <v>48</v>
+      <c r="K5" s="18" t="s">
+        <v>47</v>
       </c>
     </row>
     <row r="6" spans="1:11" s="4" customFormat="1" ht="31.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A6" s="22"/>
+      <c r="A6" s="23"/>
       <c r="B6" s="15" t="s">
         <v>44</v>
       </c>
@@ -943,17 +943,17 @@
         <v>45</v>
       </c>
       <c r="D6" s="15" t="s">
+        <v>58</v>
+      </c>
+      <c r="E6" s="15" t="s">
         <v>46</v>
       </c>
-      <c r="E6" s="15" t="s">
-        <v>47</v>
-      </c>
-      <c r="F6" s="20"/>
-      <c r="G6" s="20"/>
-      <c r="H6" s="24"/>
-      <c r="I6" s="24"/>
-      <c r="J6" s="24"/>
-      <c r="K6" s="18"/>
+      <c r="F6" s="21"/>
+      <c r="G6" s="21"/>
+      <c r="H6" s="25"/>
+      <c r="I6" s="25"/>
+      <c r="J6" s="25"/>
+      <c r="K6" s="19"/>
     </row>
     <row r="7" spans="1:11" s="2" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A7" s="16" t="s">
@@ -972,19 +972,19 @@
         <v>38</v>
       </c>
       <c r="F7" s="11" t="s">
+        <v>48</v>
+      </c>
+      <c r="G7" s="11" t="s">
         <v>49</v>
       </c>
-      <c r="G7" s="11" t="s">
+      <c r="H7" s="11" t="s">
         <v>50</v>
       </c>
-      <c r="H7" s="11" t="s">
-        <v>51</v>
-      </c>
-      <c r="I7" s="25" t="s">
+      <c r="I7" s="17" t="s">
+        <v>54</v>
+      </c>
+      <c r="J7" s="17" t="s">
         <v>55</v>
-      </c>
-      <c r="J7" s="25" t="s">
-        <v>56</v>
       </c>
       <c r="K7" s="12" t="s">
         <v>39</v>

--- a/api/templates/export/results/es.xlsx
+++ b/api/templates/export/results/es.xlsx
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="81" uniqueCount="59">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="83" uniqueCount="61">
   <si>
     <t>Code</t>
   </si>
@@ -156,9 +156,6 @@
     <t>Día del test</t>
   </si>
   <si>
-    <t>Ubicación</t>
-  </si>
-  <si>
     <t>Estado/Provincia</t>
   </si>
   <si>
@@ -202,6 +199,15 @@
   </si>
   <si>
     <t>Sitio de recolección de muestras</t>
+  </si>
+  <si>
+    <t>Código de error</t>
+  </si>
+  <si>
+    <t>&lt;errorCode&gt;</t>
+  </si>
+  <si>
+    <t>Sitio</t>
   </si>
 </sst>
 </file>
@@ -850,7 +856,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:K9"/>
+  <dimension ref="A1:L9"/>
   <sheetFormatPr defaultColWidth="11" defaultRowHeight="15.6" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="22.5" style="5" customWidth="1"/>
@@ -860,17 +866,18 @@
     <col min="5" max="5" width="28.59765625" style="9" customWidth="1"/>
     <col min="6" max="6" width="21.3984375" style="9" customWidth="1"/>
     <col min="7" max="8" width="21.296875" style="9" customWidth="1"/>
-    <col min="9" max="9" width="19" style="9" customWidth="1"/>
-    <col min="10" max="10" width="18.3984375" style="9" customWidth="1"/>
-    <col min="11" max="11" width="20.69921875" style="9" customWidth="1"/>
+    <col min="9" max="9" width="11.3984375" style="9" customWidth="1"/>
+    <col min="10" max="10" width="19" style="9" customWidth="1"/>
+    <col min="11" max="11" width="18.3984375" style="9" customWidth="1"/>
+    <col min="12" max="12" width="20.69921875" style="9" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:11" ht="21" x14ac:dyDescent="0.4">
+    <row r="1" spans="1:12" ht="21" x14ac:dyDescent="0.4">
       <c r="A1" s="6" t="s">
         <v>40</v>
       </c>
     </row>
-    <row r="2" spans="1:11" s="5" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:12" s="5" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A2" s="5" t="s">
         <v>41</v>
       </c>
@@ -884,8 +891,9 @@
       <c r="I2" s="7"/>
       <c r="J2" s="7"/>
       <c r="K2" s="7"/>
-    </row>
-    <row r="3" spans="1:11" s="5" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="L2" s="7"/>
+    </row>
+    <row r="3" spans="1:12" s="5" customFormat="1" x14ac:dyDescent="0.3">
       <c r="B3" s="7"/>
       <c r="C3" s="8"/>
       <c r="D3" s="8"/>
@@ -896,8 +904,9 @@
       <c r="I3" s="7"/>
       <c r="J3" s="7"/>
       <c r="K3" s="7"/>
-    </row>
-    <row r="4" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="L3" s="7"/>
+    </row>
+    <row r="4" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A4" s="5" t="s">
         <v>33</v>
       </c>
@@ -905,57 +914,61 @@
         <v>2</v>
       </c>
     </row>
-    <row r="5" spans="1:11" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:12" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A5" s="24" t="s">
         <v>42</v>
       </c>
       <c r="B5" s="22" t="s">
-        <v>43</v>
+        <v>57</v>
       </c>
       <c r="C5" s="23"/>
       <c r="D5" s="23"/>
       <c r="E5" s="23"/>
       <c r="F5" s="20" t="s">
+        <v>50</v>
+      </c>
+      <c r="G5" s="20" t="s">
         <v>51</v>
       </c>
-      <c r="G5" s="20" t="s">
+      <c r="H5" s="20" t="s">
         <v>52</v>
       </c>
-      <c r="H5" s="20" t="s">
-        <v>53</v>
-      </c>
       <c r="I5" s="20" t="s">
+        <v>58</v>
+      </c>
+      <c r="J5" s="20" t="s">
+        <v>55</v>
+      </c>
+      <c r="K5" s="20" t="s">
         <v>56</v>
       </c>
-      <c r="J5" s="20" t="s">
-        <v>57</v>
-      </c>
-      <c r="K5" s="18" t="s">
-        <v>47</v>
-      </c>
-    </row>
-    <row r="6" spans="1:11" s="4" customFormat="1" ht="31.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="L5" s="18" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="6" spans="1:12" s="4" customFormat="1" ht="31.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A6" s="23"/>
       <c r="B6" s="15" t="s">
+        <v>43</v>
+      </c>
+      <c r="C6" s="15" t="s">
         <v>44</v>
       </c>
-      <c r="C6" s="15" t="s">
+      <c r="D6" s="15" t="s">
+        <v>60</v>
+      </c>
+      <c r="E6" s="15" t="s">
         <v>45</v>
-      </c>
-      <c r="D6" s="15" t="s">
-        <v>58</v>
-      </c>
-      <c r="E6" s="15" t="s">
-        <v>46</v>
       </c>
       <c r="F6" s="21"/>
       <c r="G6" s="21"/>
       <c r="H6" s="25"/>
       <c r="I6" s="25"/>
       <c r="J6" s="25"/>
-      <c r="K6" s="19"/>
-    </row>
-    <row r="7" spans="1:11" s="2" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="K6" s="25"/>
+      <c r="L6" s="19"/>
+    </row>
+    <row r="7" spans="1:12" s="2" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A7" s="16" t="s">
         <v>36</v>
       </c>
@@ -972,25 +985,28 @@
         <v>38</v>
       </c>
       <c r="F7" s="11" t="s">
+        <v>47</v>
+      </c>
+      <c r="G7" s="11" t="s">
         <v>48</v>
       </c>
-      <c r="G7" s="11" t="s">
+      <c r="H7" s="11" t="s">
         <v>49</v>
       </c>
-      <c r="H7" s="11" t="s">
-        <v>50</v>
-      </c>
-      <c r="I7" s="17" t="s">
+      <c r="I7" s="11" t="s">
+        <v>59</v>
+      </c>
+      <c r="J7" s="17" t="s">
+        <v>53</v>
+      </c>
+      <c r="K7" s="17" t="s">
         <v>54</v>
       </c>
-      <c r="J7" s="17" t="s">
-        <v>55</v>
-      </c>
-      <c r="K7" s="12" t="s">
+      <c r="L7" s="12" t="s">
         <v>39</v>
       </c>
     </row>
-    <row r="9" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:12" x14ac:dyDescent="0.3">
       <c r="C9" s="13"/>
       <c r="D9" s="13"/>
       <c r="E9" s="14"/>
@@ -999,17 +1015,19 @@
       <c r="H9" s="14"/>
       <c r="I9" s="14"/>
       <c r="J9" s="14"/>
+      <c r="K9" s="14"/>
     </row>
   </sheetData>
-  <mergeCells count="8">
-    <mergeCell ref="K5:K6"/>
+  <mergeCells count="9">
+    <mergeCell ref="L5:L6"/>
     <mergeCell ref="F5:F6"/>
     <mergeCell ref="B5:E5"/>
     <mergeCell ref="A5:A6"/>
     <mergeCell ref="G5:G6"/>
     <mergeCell ref="H5:H6"/>
+    <mergeCell ref="J5:J6"/>
+    <mergeCell ref="K5:K6"/>
     <mergeCell ref="I5:I6"/>
-    <mergeCell ref="J5:J6"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup orientation="portrait" horizontalDpi="4294967292" verticalDpi="4294967292" r:id="rId1"/>

--- a/api/templates/export/results/es.xlsx
+++ b/api/templates/export/results/es.xlsx
@@ -1,15 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
-  <fileVersion appName="xl" lastEdited="6" lowestEdited="5" rupBuild="14420"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="24228"/>
   <workbookPr showInkAnnotation="0" autoCompressPictures="0"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\PROJECTS_2020\SystemOne\aspect\api\templates\export\results\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="\\wsl$\Ubuntu\home\ubuntu\aspect\api\templates\export\results\"/>
     </mc:Choice>
   </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{94F156F1-525D-4589-96F2-EB33BEDC1B5C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="480" yWindow="480" windowWidth="20736" windowHeight="11760" tabRatio="815"/>
+    <workbookView xWindow="38290" yWindow="-110" windowWidth="38620" windowHeight="21220" tabRatio="815" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Results" sheetId="1" r:id="rId1"/>
@@ -25,7 +26,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="83" uniqueCount="61">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="81" uniqueCount="59">
   <si>
     <t>Code</t>
   </si>
@@ -174,16 +175,10 @@
     <t>&lt;assayName&gt;</t>
   </si>
   <si>
-    <t>&lt;resultText&gt;</t>
-  </si>
-  <si>
     <t>Muestra ID</t>
   </si>
   <si>
     <t>Ensayo</t>
-  </si>
-  <si>
-    <t>Texto de resultado</t>
   </si>
   <si>
     <t>&lt;resultWorkflowStatus&gt;</t>
@@ -213,7 +208,7 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9" mc:Ignorable="x14ac x16r2 xr xr9">
   <fonts count="6" x14ac:knownFonts="1">
     <font>
       <sz val="12"/>
@@ -449,48 +444,48 @@
     </xf>
   </cellXfs>
   <cellStyles count="43">
-    <cellStyle name="Followed Hyperlink" xfId="2" builtinId="9" hidden="1"/>
-    <cellStyle name="Followed Hyperlink" xfId="4" builtinId="9" hidden="1"/>
-    <cellStyle name="Followed Hyperlink" xfId="6" builtinId="9" hidden="1"/>
-    <cellStyle name="Followed Hyperlink" xfId="8" builtinId="9" hidden="1"/>
-    <cellStyle name="Followed Hyperlink" xfId="10" builtinId="9" hidden="1"/>
-    <cellStyle name="Followed Hyperlink" xfId="12" builtinId="9" hidden="1"/>
-    <cellStyle name="Followed Hyperlink" xfId="14" builtinId="9" hidden="1"/>
-    <cellStyle name="Followed Hyperlink" xfId="16" builtinId="9" hidden="1"/>
-    <cellStyle name="Followed Hyperlink" xfId="18" builtinId="9" hidden="1"/>
-    <cellStyle name="Followed Hyperlink" xfId="20" builtinId="9" hidden="1"/>
-    <cellStyle name="Followed Hyperlink" xfId="22" builtinId="9" hidden="1"/>
-    <cellStyle name="Followed Hyperlink" xfId="24" builtinId="9" hidden="1"/>
-    <cellStyle name="Followed Hyperlink" xfId="26" builtinId="9" hidden="1"/>
-    <cellStyle name="Followed Hyperlink" xfId="28" builtinId="9" hidden="1"/>
-    <cellStyle name="Followed Hyperlink" xfId="30" builtinId="9" hidden="1"/>
-    <cellStyle name="Followed Hyperlink" xfId="32" builtinId="9" hidden="1"/>
-    <cellStyle name="Followed Hyperlink" xfId="34" builtinId="9" hidden="1"/>
-    <cellStyle name="Followed Hyperlink" xfId="36" builtinId="9" hidden="1"/>
-    <cellStyle name="Followed Hyperlink" xfId="38" builtinId="9" hidden="1"/>
-    <cellStyle name="Followed Hyperlink" xfId="40" builtinId="9" hidden="1"/>
-    <cellStyle name="Followed Hyperlink" xfId="42" builtinId="9" hidden="1"/>
-    <cellStyle name="Hyperlink" xfId="1" builtinId="8" hidden="1"/>
-    <cellStyle name="Hyperlink" xfId="3" builtinId="8" hidden="1"/>
-    <cellStyle name="Hyperlink" xfId="5" builtinId="8" hidden="1"/>
-    <cellStyle name="Hyperlink" xfId="7" builtinId="8" hidden="1"/>
-    <cellStyle name="Hyperlink" xfId="9" builtinId="8" hidden="1"/>
-    <cellStyle name="Hyperlink" xfId="11" builtinId="8" hidden="1"/>
-    <cellStyle name="Hyperlink" xfId="13" builtinId="8" hidden="1"/>
-    <cellStyle name="Hyperlink" xfId="15" builtinId="8" hidden="1"/>
-    <cellStyle name="Hyperlink" xfId="17" builtinId="8" hidden="1"/>
-    <cellStyle name="Hyperlink" xfId="19" builtinId="8" hidden="1"/>
-    <cellStyle name="Hyperlink" xfId="21" builtinId="8" hidden="1"/>
-    <cellStyle name="Hyperlink" xfId="23" builtinId="8" hidden="1"/>
-    <cellStyle name="Hyperlink" xfId="25" builtinId="8" hidden="1"/>
-    <cellStyle name="Hyperlink" xfId="27" builtinId="8" hidden="1"/>
-    <cellStyle name="Hyperlink" xfId="29" builtinId="8" hidden="1"/>
-    <cellStyle name="Hyperlink" xfId="31" builtinId="8" hidden="1"/>
-    <cellStyle name="Hyperlink" xfId="33" builtinId="8" hidden="1"/>
-    <cellStyle name="Hyperlink" xfId="35" builtinId="8" hidden="1"/>
-    <cellStyle name="Hyperlink" xfId="37" builtinId="8" hidden="1"/>
-    <cellStyle name="Hyperlink" xfId="39" builtinId="8" hidden="1"/>
-    <cellStyle name="Hyperlink" xfId="41" builtinId="8" hidden="1"/>
+    <cellStyle name="Hipervínculo" xfId="1" builtinId="8" hidden="1"/>
+    <cellStyle name="Hipervínculo" xfId="3" builtinId="8" hidden="1"/>
+    <cellStyle name="Hipervínculo" xfId="5" builtinId="8" hidden="1"/>
+    <cellStyle name="Hipervínculo" xfId="7" builtinId="8" hidden="1"/>
+    <cellStyle name="Hipervínculo" xfId="9" builtinId="8" hidden="1"/>
+    <cellStyle name="Hipervínculo" xfId="11" builtinId="8" hidden="1"/>
+    <cellStyle name="Hipervínculo" xfId="13" builtinId="8" hidden="1"/>
+    <cellStyle name="Hipervínculo" xfId="15" builtinId="8" hidden="1"/>
+    <cellStyle name="Hipervínculo" xfId="17" builtinId="8" hidden="1"/>
+    <cellStyle name="Hipervínculo" xfId="19" builtinId="8" hidden="1"/>
+    <cellStyle name="Hipervínculo" xfId="21" builtinId="8" hidden="1"/>
+    <cellStyle name="Hipervínculo" xfId="23" builtinId="8" hidden="1"/>
+    <cellStyle name="Hipervínculo" xfId="25" builtinId="8" hidden="1"/>
+    <cellStyle name="Hipervínculo" xfId="27" builtinId="8" hidden="1"/>
+    <cellStyle name="Hipervínculo" xfId="29" builtinId="8" hidden="1"/>
+    <cellStyle name="Hipervínculo" xfId="31" builtinId="8" hidden="1"/>
+    <cellStyle name="Hipervínculo" xfId="33" builtinId="8" hidden="1"/>
+    <cellStyle name="Hipervínculo" xfId="35" builtinId="8" hidden="1"/>
+    <cellStyle name="Hipervínculo" xfId="37" builtinId="8" hidden="1"/>
+    <cellStyle name="Hipervínculo" xfId="39" builtinId="8" hidden="1"/>
+    <cellStyle name="Hipervínculo" xfId="41" builtinId="8" hidden="1"/>
+    <cellStyle name="Hipervínculo visitado" xfId="2" builtinId="9" hidden="1"/>
+    <cellStyle name="Hipervínculo visitado" xfId="4" builtinId="9" hidden="1"/>
+    <cellStyle name="Hipervínculo visitado" xfId="6" builtinId="9" hidden="1"/>
+    <cellStyle name="Hipervínculo visitado" xfId="8" builtinId="9" hidden="1"/>
+    <cellStyle name="Hipervínculo visitado" xfId="10" builtinId="9" hidden="1"/>
+    <cellStyle name="Hipervínculo visitado" xfId="12" builtinId="9" hidden="1"/>
+    <cellStyle name="Hipervínculo visitado" xfId="14" builtinId="9" hidden="1"/>
+    <cellStyle name="Hipervínculo visitado" xfId="16" builtinId="9" hidden="1"/>
+    <cellStyle name="Hipervínculo visitado" xfId="18" builtinId="9" hidden="1"/>
+    <cellStyle name="Hipervínculo visitado" xfId="20" builtinId="9" hidden="1"/>
+    <cellStyle name="Hipervínculo visitado" xfId="22" builtinId="9" hidden="1"/>
+    <cellStyle name="Hipervínculo visitado" xfId="24" builtinId="9" hidden="1"/>
+    <cellStyle name="Hipervínculo visitado" xfId="26" builtinId="9" hidden="1"/>
+    <cellStyle name="Hipervínculo visitado" xfId="28" builtinId="9" hidden="1"/>
+    <cellStyle name="Hipervínculo visitado" xfId="30" builtinId="9" hidden="1"/>
+    <cellStyle name="Hipervínculo visitado" xfId="32" builtinId="9" hidden="1"/>
+    <cellStyle name="Hipervínculo visitado" xfId="34" builtinId="9" hidden="1"/>
+    <cellStyle name="Hipervínculo visitado" xfId="36" builtinId="9" hidden="1"/>
+    <cellStyle name="Hipervínculo visitado" xfId="38" builtinId="9" hidden="1"/>
+    <cellStyle name="Hipervínculo visitado" xfId="40" builtinId="9" hidden="1"/>
+    <cellStyle name="Hipervínculo visitado" xfId="42" builtinId="9" hidden="1"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="2">
@@ -518,7 +513,7 @@
     </dxf>
   </dxfs>
   <tableStyles count="1" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleMedium4">
-    <tableStyle name="MySqlDefault" pivot="0" table="0" count="2">
+    <tableStyle name="MySqlDefault" pivot="0" table="0" count="2" xr9:uid="{00000000-0011-0000-FFFF-FFFF00000000}">
       <tableStyleElement type="wholeTable" dxfId="1"/>
       <tableStyleElement type="headerRow" dxfId="0"/>
     </tableStyle>
@@ -855,29 +850,29 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:L9"/>
-  <sheetFormatPr defaultColWidth="11" defaultRowHeight="15.6" x14ac:dyDescent="0.3"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+  <dimension ref="A1:K9"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="11" defaultRowHeight="15.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="22.5" style="5" customWidth="1"/>
-    <col min="2" max="2" width="23.09765625" style="7" customWidth="1"/>
-    <col min="3" max="3" width="22.3984375" style="8" customWidth="1"/>
+    <col min="2" max="2" width="23.08203125" style="7" customWidth="1"/>
+    <col min="3" max="3" width="22.4140625" style="8" customWidth="1"/>
     <col min="4" max="4" width="18.5" style="8" customWidth="1"/>
-    <col min="5" max="5" width="28.59765625" style="9" customWidth="1"/>
-    <col min="6" max="6" width="21.3984375" style="9" customWidth="1"/>
-    <col min="7" max="8" width="21.296875" style="9" customWidth="1"/>
-    <col min="9" max="9" width="11.3984375" style="9" customWidth="1"/>
-    <col min="10" max="10" width="19" style="9" customWidth="1"/>
-    <col min="11" max="11" width="18.3984375" style="9" customWidth="1"/>
-    <col min="12" max="12" width="20.69921875" style="9" customWidth="1"/>
+    <col min="5" max="5" width="28.58203125" style="9" customWidth="1"/>
+    <col min="6" max="6" width="21.4140625" style="9" customWidth="1"/>
+    <col min="7" max="7" width="21.33203125" style="9" customWidth="1"/>
+    <col min="8" max="8" width="11.4140625" style="9" customWidth="1"/>
+    <col min="9" max="9" width="19" style="9" customWidth="1"/>
+    <col min="10" max="10" width="18.4140625" style="9" customWidth="1"/>
+    <col min="11" max="11" width="20.6640625" style="9" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:12" ht="21" x14ac:dyDescent="0.4">
+    <row r="1" spans="1:11" ht="21" x14ac:dyDescent="0.5">
       <c r="A1" s="6" t="s">
         <v>40</v>
       </c>
     </row>
-    <row r="2" spans="1:12" s="5" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:11" s="5" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A2" s="5" t="s">
         <v>41</v>
       </c>
@@ -891,9 +886,8 @@
       <c r="I2" s="7"/>
       <c r="J2" s="7"/>
       <c r="K2" s="7"/>
-      <c r="L2" s="7"/>
-    </row>
-    <row r="3" spans="1:12" s="5" customFormat="1" x14ac:dyDescent="0.3">
+    </row>
+    <row r="3" spans="1:11" s="5" customFormat="1" x14ac:dyDescent="0.35">
       <c r="B3" s="7"/>
       <c r="C3" s="8"/>
       <c r="D3" s="8"/>
@@ -904,9 +898,8 @@
       <c r="I3" s="7"/>
       <c r="J3" s="7"/>
       <c r="K3" s="7"/>
-      <c r="L3" s="7"/>
-    </row>
-    <row r="4" spans="1:12" x14ac:dyDescent="0.3">
+    </row>
+    <row r="4" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A4" s="5" t="s">
         <v>33</v>
       </c>
@@ -914,39 +907,36 @@
         <v>2</v>
       </c>
     </row>
-    <row r="5" spans="1:12" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:11" ht="30" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A5" s="24" t="s">
         <v>42</v>
       </c>
       <c r="B5" s="22" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="C5" s="23"/>
       <c r="D5" s="23"/>
       <c r="E5" s="23"/>
       <c r="F5" s="20" t="s">
+        <v>49</v>
+      </c>
+      <c r="G5" s="20" t="s">
         <v>50</v>
       </c>
-      <c r="G5" s="20" t="s">
-        <v>51</v>
-      </c>
       <c r="H5" s="20" t="s">
-        <v>52</v>
+        <v>56</v>
       </c>
       <c r="I5" s="20" t="s">
-        <v>58</v>
+        <v>53</v>
       </c>
       <c r="J5" s="20" t="s">
-        <v>55</v>
-      </c>
-      <c r="K5" s="20" t="s">
-        <v>56</v>
-      </c>
-      <c r="L5" s="18" t="s">
+        <v>54</v>
+      </c>
+      <c r="K5" s="18" t="s">
         <v>46</v>
       </c>
     </row>
-    <row r="6" spans="1:12" s="4" customFormat="1" ht="31.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:11" s="4" customFormat="1" ht="31.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A6" s="23"/>
       <c r="B6" s="15" t="s">
         <v>43</v>
@@ -955,7 +945,7 @@
         <v>44</v>
       </c>
       <c r="D6" s="15" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="E6" s="15" t="s">
         <v>45</v>
@@ -965,10 +955,9 @@
       <c r="H6" s="25"/>
       <c r="I6" s="25"/>
       <c r="J6" s="25"/>
-      <c r="K6" s="25"/>
-      <c r="L6" s="19"/>
-    </row>
-    <row r="7" spans="1:12" s="2" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="K6" s="19"/>
+    </row>
+    <row r="7" spans="1:11" s="2" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A7" s="16" t="s">
         <v>36</v>
       </c>
@@ -991,22 +980,19 @@
         <v>48</v>
       </c>
       <c r="H7" s="11" t="s">
-        <v>49</v>
-      </c>
-      <c r="I7" s="11" t="s">
-        <v>59</v>
+        <v>57</v>
+      </c>
+      <c r="I7" s="17" t="s">
+        <v>51</v>
       </c>
       <c r="J7" s="17" t="s">
-        <v>53</v>
-      </c>
-      <c r="K7" s="17" t="s">
-        <v>54</v>
-      </c>
-      <c r="L7" s="12" t="s">
+        <v>52</v>
+      </c>
+      <c r="K7" s="12" t="s">
         <v>39</v>
       </c>
     </row>
-    <row r="9" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:11" x14ac:dyDescent="0.35">
       <c r="C9" s="13"/>
       <c r="D9" s="13"/>
       <c r="E9" s="14"/>
@@ -1015,19 +1001,17 @@
       <c r="H9" s="14"/>
       <c r="I9" s="14"/>
       <c r="J9" s="14"/>
-      <c r="K9" s="14"/>
     </row>
   </sheetData>
-  <mergeCells count="9">
-    <mergeCell ref="L5:L6"/>
+  <mergeCells count="8">
+    <mergeCell ref="K5:K6"/>
     <mergeCell ref="F5:F6"/>
     <mergeCell ref="B5:E5"/>
     <mergeCell ref="A5:A6"/>
     <mergeCell ref="G5:G6"/>
+    <mergeCell ref="I5:I6"/>
+    <mergeCell ref="J5:J6"/>
     <mergeCell ref="H5:H6"/>
-    <mergeCell ref="J5:J6"/>
-    <mergeCell ref="K5:K6"/>
-    <mergeCell ref="I5:I6"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup orientation="portrait" horizontalDpi="4294967292" verticalDpi="4294967292" r:id="rId1"/>
@@ -1040,16 +1024,16 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:C27"/>
-  <sheetFormatPr defaultColWidth="8.59765625" defaultRowHeight="22.05" customHeight="1" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.58203125" defaultRowHeight="22" customHeight="1" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="5.09765625" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="39.19921875" customWidth="1"/>
-    <col min="3" max="3" width="100.59765625" customWidth="1"/>
+    <col min="1" max="1" width="5.08203125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="39.1640625" customWidth="1"/>
+    <col min="3" max="3" width="100.58203125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" ht="22.05" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:3" ht="22" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1060,7 +1044,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:3" ht="22.05" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:3" ht="22" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A2" s="3">
         <v>1001</v>
       </c>
@@ -1071,7 +1055,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="3" spans="1:3" ht="22.05" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:3" ht="22" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A3" s="3">
         <v>1002</v>
       </c>
@@ -1082,7 +1066,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="4" spans="1:3" ht="22.05" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:3" ht="22" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A4" s="3">
         <v>1004</v>
       </c>
@@ -1093,7 +1077,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="5" spans="1:3" ht="22.05" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:3" ht="22" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A5" s="3">
         <v>1005</v>
       </c>
@@ -1104,7 +1088,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="6" spans="1:3" ht="22.05" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:3" ht="22" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A6" s="3">
         <v>1006</v>
       </c>
@@ -1115,7 +1099,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="7" spans="1:3" ht="22.05" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:3" ht="22" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A7" s="3">
         <v>1007</v>
       </c>
@@ -1126,7 +1110,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="8" spans="1:3" ht="22.05" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:3" ht="22" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A8" s="3">
         <v>1017</v>
       </c>
@@ -1137,7 +1121,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="9" spans="1:3" ht="22.05" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:3" ht="22" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A9" s="3">
         <v>1018</v>
       </c>
@@ -1148,7 +1132,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="10" spans="1:3" ht="22.05" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:3" ht="22" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A10" s="3">
         <v>2003</v>
       </c>
@@ -1159,7 +1143,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="11" spans="1:3" ht="22.05" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:3" ht="22" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A11" s="3">
         <v>2005</v>
       </c>
@@ -1170,7 +1154,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="12" spans="1:3" ht="22.05" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:3" ht="22" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A12" s="3">
         <v>2008</v>
       </c>
@@ -1181,7 +1165,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="13" spans="1:3" ht="22.05" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:3" ht="22" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A13" s="3">
         <v>2009</v>
       </c>
@@ -1192,7 +1176,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="14" spans="1:3" ht="22.05" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:3" ht="22" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A14" s="3">
         <v>2011</v>
       </c>
@@ -1203,7 +1187,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="15" spans="1:3" ht="22.05" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:3" ht="22" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A15" s="3">
         <v>2014</v>
       </c>
@@ -1214,7 +1198,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="16" spans="1:3" ht="22.05" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:3" ht="22" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A16" s="3">
         <v>2016</v>
       </c>
@@ -1225,7 +1209,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="17" spans="1:3" ht="22.05" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:3" ht="22" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A17" s="3">
         <v>2018</v>
       </c>
@@ -1236,7 +1220,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="18" spans="1:3" ht="22.05" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:3" ht="22" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A18" s="3">
         <v>2022</v>
       </c>
@@ -1247,7 +1231,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="19" spans="1:3" ht="22.05" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:3" ht="22" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A19" s="3">
         <v>2025</v>
       </c>
@@ -1258,7 +1242,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="20" spans="1:3" ht="22.05" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:3" ht="22" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A20" s="3">
         <v>2032</v>
       </c>
@@ -1269,7 +1253,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="21" spans="1:3" ht="22.05" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:3" ht="22" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A21" s="3">
         <v>2034</v>
       </c>
@@ -1280,7 +1264,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="22" spans="1:3" ht="22.05" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:3" ht="22" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A22" s="3">
         <v>2037</v>
       </c>
@@ -1291,7 +1275,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="23" spans="1:3" ht="22.05" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:3" ht="22" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A23" s="3">
         <v>4010</v>
       </c>
@@ -1302,7 +1286,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="24" spans="1:3" ht="22.05" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:3" ht="22" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A24" s="3">
         <v>4017</v>
       </c>
@@ -1313,7 +1297,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="25" spans="1:3" ht="22.05" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:3" ht="22" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A25" s="3">
         <v>5006</v>
       </c>
@@ -1324,7 +1308,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="26" spans="1:3" ht="22.05" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:3" ht="22" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A26" s="3">
         <v>5007</v>
       </c>
@@ -1335,7 +1319,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="27" spans="1:3" ht="22.05" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:3" ht="22" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A27" s="3">
         <v>5011</v>
       </c>

--- a/api/templates/export/results/es.xlsx
+++ b/api/templates/export/results/es.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="24228"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="24701"/>
   <workbookPr showInkAnnotation="0" autoCompressPictures="0"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="\\wsl$\Ubuntu\home\ubuntu\aspect\api\templates\export\results\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="\\wsl.localhost\Ubuntu-20.04\home\ubuntu\aspect\api\templates\all_results\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{94F156F1-525D-4589-96F2-EB33BEDC1B5C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{99F4BA0C-E35A-4229-A07D-2E18FEF8198E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="38290" yWindow="-110" windowWidth="38620" windowHeight="21220" tabRatio="815" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="5000" yWindow="5000" windowWidth="28800" windowHeight="15410" tabRatio="815" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Results" sheetId="1" r:id="rId1"/>
@@ -26,7 +26,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="81" uniqueCount="59">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="82" uniqueCount="60">
   <si>
     <t>Code</t>
   </si>
@@ -151,9 +151,6 @@
     <t>Resultados</t>
   </si>
   <si>
-    <t>Impreso &lt;date&gt;</t>
-  </si>
-  <si>
     <t>Día del test</t>
   </si>
   <si>
@@ -203,13 +200,19 @@
   </si>
   <si>
     <t>Sitio</t>
+  </si>
+  <si>
+    <t>Impreso &lt;Dates&gt;</t>
+  </si>
+  <si>
+    <t>Hay &lt;PerformanceTotalRecordLimit&gt; mas registros disponibles en la base de datos, pero por problemas de performance hemos limitado a &lt;PerformanceQueryLimit&gt; registros. Si requiere mas registros por favor vuelva a obtener el reporte utilizando otros filtros</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9" mc:Ignorable="x14ac x16r2 xr xr9">
-  <fonts count="6" x14ac:knownFonts="1">
+  <fonts count="7" x14ac:knownFonts="1">
     <font>
       <sz val="12"/>
       <color theme="1"/>
@@ -257,8 +260,15 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C0006"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
-  <fills count="3">
+  <fills count="4">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -269,6 +279,11 @@
       <patternFill patternType="solid">
         <fgColor theme="6" tint="0.59999389629810485"/>
         <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC7CE"/>
       </patternFill>
     </fill>
   </fills>
@@ -322,7 +337,7 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="43">
+  <cellStyleXfs count="44">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
@@ -366,8 +381,9 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="26">
+  <cellXfs count="27">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
@@ -442,8 +458,11 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="0" xfId="43" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
   </cellXfs>
-  <cellStyles count="43">
+  <cellStyles count="44">
     <cellStyle name="Hipervínculo" xfId="1" builtinId="8" hidden="1"/>
     <cellStyle name="Hipervínculo" xfId="3" builtinId="8" hidden="1"/>
     <cellStyle name="Hipervínculo" xfId="5" builtinId="8" hidden="1"/>
@@ -486,6 +505,7 @@
     <cellStyle name="Hipervínculo visitado" xfId="38" builtinId="9" hidden="1"/>
     <cellStyle name="Hipervínculo visitado" xfId="40" builtinId="9" hidden="1"/>
     <cellStyle name="Hipervínculo visitado" xfId="42" builtinId="9" hidden="1"/>
+    <cellStyle name="Incorrecto" xfId="43" builtinId="27"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="2">
@@ -851,7 +871,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:K9"/>
+  <dimension ref="A1:K11"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="11" defaultRowHeight="15.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="22.5" style="5" customWidth="1"/>
@@ -874,7 +894,7 @@
     </row>
     <row r="2" spans="1:11" s="5" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A2" s="5" t="s">
-        <v>41</v>
+        <v>58</v>
       </c>
       <c r="B2" s="7"/>
       <c r="C2" s="8"/>
@@ -887,17 +907,20 @@
       <c r="J2" s="7"/>
       <c r="K2" s="7"/>
     </row>
-    <row r="3" spans="1:11" s="5" customFormat="1" x14ac:dyDescent="0.35">
-      <c r="B3" s="7"/>
-      <c r="C3" s="8"/>
-      <c r="D3" s="8"/>
-      <c r="E3" s="7"/>
-      <c r="F3" s="7"/>
-      <c r="G3" s="7"/>
-      <c r="H3" s="7"/>
-      <c r="I3" s="7"/>
-      <c r="J3" s="7"/>
-      <c r="K3" s="7"/>
+    <row r="3" spans="1:11" s="5" customFormat="1" ht="22" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A3" s="26" t="s">
+        <v>59</v>
+      </c>
+      <c r="B3" s="26"/>
+      <c r="C3" s="26"/>
+      <c r="D3" s="26"/>
+      <c r="E3" s="26"/>
+      <c r="F3" s="26"/>
+      <c r="G3" s="26"/>
+      <c r="H3" s="26"/>
+      <c r="I3" s="26"/>
+      <c r="J3" s="26"/>
+      <c r="K3" s="26"/>
     </row>
     <row r="4" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A4" s="5" t="s">
@@ -909,46 +932,46 @@
     </row>
     <row r="5" spans="1:11" ht="30" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A5" s="24" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="B5" s="22" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="C5" s="23"/>
       <c r="D5" s="23"/>
       <c r="E5" s="23"/>
       <c r="F5" s="20" t="s">
+        <v>48</v>
+      </c>
+      <c r="G5" s="20" t="s">
         <v>49</v>
       </c>
-      <c r="G5" s="20" t="s">
-        <v>50</v>
-      </c>
       <c r="H5" s="20" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="I5" s="20" t="s">
+        <v>52</v>
+      </c>
+      <c r="J5" s="20" t="s">
         <v>53</v>
       </c>
-      <c r="J5" s="20" t="s">
-        <v>54</v>
-      </c>
       <c r="K5" s="18" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
     </row>
     <row r="6" spans="1:11" s="4" customFormat="1" ht="31.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A6" s="23"/>
       <c r="B6" s="15" t="s">
+        <v>42</v>
+      </c>
+      <c r="C6" s="15" t="s">
         <v>43</v>
       </c>
-      <c r="C6" s="15" t="s">
+      <c r="D6" s="15" t="s">
+        <v>57</v>
+      </c>
+      <c r="E6" s="15" t="s">
         <v>44</v>
-      </c>
-      <c r="D6" s="15" t="s">
-        <v>58</v>
-      </c>
-      <c r="E6" s="15" t="s">
-        <v>45</v>
       </c>
       <c r="F6" s="21"/>
       <c r="G6" s="21"/>
@@ -974,19 +997,19 @@
         <v>38</v>
       </c>
       <c r="F7" s="11" t="s">
+        <v>46</v>
+      </c>
+      <c r="G7" s="11" t="s">
         <v>47</v>
       </c>
-      <c r="G7" s="11" t="s">
-        <v>48</v>
-      </c>
       <c r="H7" s="11" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="I7" s="17" t="s">
+        <v>50</v>
+      </c>
+      <c r="J7" s="17" t="s">
         <v>51</v>
-      </c>
-      <c r="J7" s="17" t="s">
-        <v>52</v>
       </c>
       <c r="K7" s="12" t="s">
         <v>39</v>
@@ -1002,8 +1025,12 @@
       <c r="I9" s="14"/>
       <c r="J9" s="14"/>
     </row>
+    <row r="11" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="D11" s="13"/>
+    </row>
   </sheetData>
-  <mergeCells count="8">
+  <mergeCells count="9">
+    <mergeCell ref="A3:K3"/>
     <mergeCell ref="K5:K6"/>
     <mergeCell ref="F5:F6"/>
     <mergeCell ref="B5:E5"/>

--- a/api/templates/export/results/es.xlsx
+++ b/api/templates/export/results/es.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="24701"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="25225"/>
   <workbookPr showInkAnnotation="0" autoCompressPictures="0"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="\\wsl.localhost\Ubuntu-20.04\home\ubuntu\aspect\api\templates\all_results\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\aepel\Desktop\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{99F4BA0C-E35A-4229-A07D-2E18FEF8198E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{93F1F369-E79A-4DA7-8266-21B69B3D90F9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="5000" yWindow="5000" windowWidth="28800" windowHeight="15410" tabRatio="815" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-38020" yWindow="380" windowWidth="28800" windowHeight="15370" tabRatio="815" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Results" sheetId="1" r:id="rId1"/>
@@ -26,7 +26,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="82" uniqueCount="60">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="81" uniqueCount="59">
   <si>
     <t>Code</t>
   </si>
@@ -188,9 +188,6 @@
   </si>
   <si>
     <t>Estado del tratamiento</t>
-  </si>
-  <si>
-    <t>Sitio de recolección de muestras</t>
   </si>
   <si>
     <t>Código de error</t>
@@ -287,7 +284,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="4">
+  <borders count="3">
     <border>
       <left/>
       <right/>
@@ -323,19 +320,6 @@
       <bottom/>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin">
-        <color auto="1"/>
-      </left>
-      <right style="thin">
-        <color auto="1"/>
-      </right>
-      <top/>
-      <bottom style="thin">
-        <color auto="1"/>
-      </bottom>
-      <diagonal/>
-    </border>
   </borders>
   <cellStyleXfs count="44">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
@@ -383,7 +367,7 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="6" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="27">
+  <cellXfs count="22">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
@@ -434,32 +418,17 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="6" fillId="3" borderId="0" xfId="43" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="44">
@@ -871,7 +840,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:K11"/>
+  <dimension ref="A1:K10"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="11" defaultRowHeight="15.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="22.5" style="5" customWidth="1"/>
@@ -894,7 +863,7 @@
     </row>
     <row r="2" spans="1:11" s="5" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A2" s="5" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="B2" s="7"/>
       <c r="C2" s="8"/>
@@ -908,38 +877,44 @@
       <c r="K2" s="7"/>
     </row>
     <row r="3" spans="1:11" s="5" customFormat="1" ht="22" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A3" s="26" t="s">
-        <v>59</v>
-      </c>
-      <c r="B3" s="26"/>
-      <c r="C3" s="26"/>
-      <c r="D3" s="26"/>
-      <c r="E3" s="26"/>
-      <c r="F3" s="26"/>
-      <c r="G3" s="26"/>
-      <c r="H3" s="26"/>
-      <c r="I3" s="26"/>
-      <c r="J3" s="26"/>
-      <c r="K3" s="26"/>
+      <c r="A3" s="18" t="s">
+        <v>58</v>
+      </c>
+      <c r="B3" s="18"/>
+      <c r="C3" s="18"/>
+      <c r="D3" s="18"/>
+      <c r="E3" s="18"/>
+      <c r="F3" s="18"/>
+      <c r="G3" s="18"/>
+      <c r="H3" s="18"/>
+      <c r="I3" s="18"/>
+      <c r="J3" s="18"/>
+      <c r="K3" s="18"/>
     </row>
     <row r="4" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A4" s="5" t="s">
         <v>33</v>
       </c>
       <c r="B4" s="7">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="5" spans="1:11" ht="30" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A5" s="24" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="5" spans="1:11" s="4" customFormat="1" ht="31.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A5" s="19" t="s">
         <v>41</v>
       </c>
-      <c r="B5" s="22" t="s">
-        <v>54</v>
-      </c>
-      <c r="C5" s="23"/>
-      <c r="D5" s="23"/>
-      <c r="E5" s="23"/>
+      <c r="B5" s="15" t="s">
+        <v>42</v>
+      </c>
+      <c r="C5" s="15" t="s">
+        <v>43</v>
+      </c>
+      <c r="D5" s="15" t="s">
+        <v>56</v>
+      </c>
+      <c r="E5" s="15" t="s">
+        <v>44</v>
+      </c>
       <c r="F5" s="20" t="s">
         <v>48</v>
       </c>
@@ -947,7 +922,7 @@
         <v>49</v>
       </c>
       <c r="H5" s="20" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="I5" s="20" t="s">
         <v>52</v>
@@ -955,90 +930,61 @@
       <c r="J5" s="20" t="s">
         <v>53</v>
       </c>
-      <c r="K5" s="18" t="s">
+      <c r="K5" s="21" t="s">
         <v>45</v>
       </c>
     </row>
-    <row r="6" spans="1:11" s="4" customFormat="1" ht="31.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A6" s="23"/>
-      <c r="B6" s="15" t="s">
-        <v>42</v>
-      </c>
-      <c r="C6" s="15" t="s">
-        <v>43</v>
-      </c>
-      <c r="D6" s="15" t="s">
-        <v>57</v>
-      </c>
-      <c r="E6" s="15" t="s">
-        <v>44</v>
-      </c>
-      <c r="F6" s="21"/>
-      <c r="G6" s="21"/>
-      <c r="H6" s="25"/>
-      <c r="I6" s="25"/>
-      <c r="J6" s="25"/>
-      <c r="K6" s="19"/>
-    </row>
-    <row r="7" spans="1:11" s="2" customFormat="1" x14ac:dyDescent="0.35">
-      <c r="A7" s="16" t="s">
+    <row r="6" spans="1:11" s="2" customFormat="1" x14ac:dyDescent="0.35">
+      <c r="A6" s="16" t="s">
         <v>36</v>
       </c>
-      <c r="B7" s="10" t="s">
+      <c r="B6" s="10" t="s">
         <v>34</v>
       </c>
-      <c r="C7" s="10" t="s">
+      <c r="C6" s="10" t="s">
         <v>35</v>
       </c>
-      <c r="D7" s="10" t="s">
+      <c r="D6" s="10" t="s">
         <v>37</v>
       </c>
-      <c r="E7" s="11" t="s">
+      <c r="E6" s="11" t="s">
         <v>38</v>
       </c>
-      <c r="F7" s="11" t="s">
+      <c r="F6" s="11" t="s">
         <v>46</v>
       </c>
-      <c r="G7" s="11" t="s">
+      <c r="G6" s="11" t="s">
         <v>47</v>
       </c>
-      <c r="H7" s="11" t="s">
-        <v>56</v>
-      </c>
-      <c r="I7" s="17" t="s">
+      <c r="H6" s="11" t="s">
+        <v>55</v>
+      </c>
+      <c r="I6" s="17" t="s">
         <v>50</v>
       </c>
-      <c r="J7" s="17" t="s">
+      <c r="J6" s="17" t="s">
         <v>51</v>
       </c>
-      <c r="K7" s="12" t="s">
+      <c r="K6" s="12" t="s">
         <v>39</v>
       </c>
     </row>
-    <row r="9" spans="1:11" x14ac:dyDescent="0.35">
-      <c r="C9" s="13"/>
-      <c r="D9" s="13"/>
-      <c r="E9" s="14"/>
-      <c r="F9" s="14"/>
-      <c r="G9" s="14"/>
-      <c r="H9" s="14"/>
-      <c r="I9" s="14"/>
-      <c r="J9" s="14"/>
-    </row>
-    <row r="11" spans="1:11" x14ac:dyDescent="0.35">
-      <c r="D11" s="13"/>
+    <row r="8" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="C8" s="13"/>
+      <c r="D8" s="13"/>
+      <c r="E8" s="14"/>
+      <c r="F8" s="14"/>
+      <c r="G8" s="14"/>
+      <c r="H8" s="14"/>
+      <c r="I8" s="14"/>
+      <c r="J8" s="14"/>
+    </row>
+    <row r="10" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="D10" s="13"/>
     </row>
   </sheetData>
-  <mergeCells count="9">
+  <mergeCells count="1">
     <mergeCell ref="A3:K3"/>
-    <mergeCell ref="K5:K6"/>
-    <mergeCell ref="F5:F6"/>
-    <mergeCell ref="B5:E5"/>
-    <mergeCell ref="A5:A6"/>
-    <mergeCell ref="G5:G6"/>
-    <mergeCell ref="I5:I6"/>
-    <mergeCell ref="J5:J6"/>
-    <mergeCell ref="H5:H6"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup orientation="portrait" horizontalDpi="4294967292" verticalDpi="4294967292" r:id="rId1"/>
